--- a/src/Excelsior.Tests/TypeInferenceTests.TemplateInfersDateValidation.verified.xlsx
+++ b/src/Excelsior.Tests/TypeInferenceTests.TemplateInfersDateValidation.verified.xlsx
@@ -9,9 +9,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-MM-dd HH:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="yyyy-MM-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-MM-dd HH:mm:ss z"/>
+    <numFmt numFmtId="166" formatCode="yyyy-MM-dd"/>
+    <numFmt numFmtId="167" formatCode="HH:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -41,11 +43,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0"/>
     <xf fontId="1" fillId="0" borderId="0" applyFont="1" applyFill="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0"/>
   </cellXfs>
   <dxfs count="1">
     <dxf>
@@ -63,9 +67,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="13" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9" style="3" customWidth="1"/>
-    <col min="3" max="3" width="16" style="3" customWidth="1"/>
-    <col min="4" max="4" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="10" style="3" customWidth="1"/>
+    <col min="3" max="3" width="9" style="4" customWidth="1"/>
+    <col min="4" max="4" width="16" style="4" customWidth="1"/>
+    <col min="5" max="5" width="9" style="5" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -76,22 +82,32 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Day</t>
+          <t xml:space="preserve">Offset</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Day</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">OptionalDay</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clock</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bounded</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1"/>
+  <autoFilter ref="A1:F1"/>
   <conditionalFormatting sqref="A2:A6">
     <cfRule type="containsBlanks" dxfId="0" priority="1">
       <formula>LEN(TRIM(A2))=0</formula>
@@ -102,25 +118,43 @@
       <formula>LEN(TRIM(B2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D6">
+  <conditionalFormatting sqref="C2:C6">
     <cfRule type="containsBlanks" dxfId="0" priority="3">
-      <formula>LEN(TRIM(D2))=0</formula>
+      <formula>LEN(TRIM(C2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
-    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date." prompt="Required field" sqref="A2:A6">
+  <conditionalFormatting sqref="E2:E6">
+    <cfRule type="containsBlanks" dxfId="0" priority="4">
+      <formula>LEN(TRIM(E2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="containsBlanks" dxfId="0" priority="5">
+      <formula>LEN(TRIM(F2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="6">
+    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time (yyyy-MM-dd HH:mm:ss)." prompt="Required field" sqref="A2:A6">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date." prompt="Required field" sqref="B2:B6">
+    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time (yyyy-MM-dd HH:mm:ss z)." prompt="Required field" sqref="B2:B6">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date." sqref="C2:C6">
+    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date (yyyy-MM-dd)." prompt="Required field" sqref="C2:C6">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a date between 2020-01-01 and 2020-12-31." prompt="Date between 2020-01-01 and 2020-12-31" sqref="D2:D6">
+    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date (yyyy-MM-dd)." sqref="D2:D6">
+      <formula1>2</formula1>
+      <formula2>2958465</formula2>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid time (HH:mm:ss)." prompt="Required field" sqref="E2:E6">
+      <formula1>2</formula1>
+      <formula2>2958465</formula2>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a date between 2020-01-01 and 2020-12-31." prompt="Date between 2020-01-01 and 2020-12-31" sqref="F2:F6">
       <formula1>43831</formula1>
       <formula2>44196</formula2>
     </dataValidation>
@@ -132,9 +166,11 @@
 <columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
   <sheet name="Events">
     <column index="1" property="Timestamp"/>
-    <column index="2" property="Day"/>
-    <column index="3" property="OptionalDay"/>
-    <column index="4" property="Bounded"/>
+    <column index="2" property="Offset"/>
+    <column index="3" property="Day"/>
+    <column index="4" property="OptionalDay"/>
+    <column index="5" property="Clock"/>
+    <column index="6" property="Bounded"/>
   </sheet>
 </columnMetadata>
 </file>
--- a/src/Excelsior.Tests/TypeInferenceTests.TemplateInfersDateValidation.verified.xlsx
+++ b/src/Excelsior.Tests/TypeInferenceTests.TemplateInfersDateValidation.verified.xlsx
@@ -134,23 +134,23 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
-    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time (yyyy-MM-dd HH:mm:ss)." prompt="Required field" sqref="A2:A6">
+    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time.&#10;yyyy-MM-dd HH:mm:ss" prompt="Required field" sqref="A2:A6">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time (yyyy-MM-dd HH:mm:ss z)." prompt="Required field" sqref="B2:B6">
+    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time.&#10;yyyy-MM-dd HH:mm:ss z" prompt="Required field" sqref="B2:B6">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date (yyyy-MM-dd)." prompt="Required field" sqref="C2:C6">
+    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date.&#10;yyyy-MM-dd" prompt="Required field" sqref="C2:C6">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date (yyyy-MM-dd)." sqref="D2:D6">
+    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date.&#10;yyyy-MM-dd" sqref="D2:D6">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid time (HH:mm:ss)." prompt="Required field" sqref="E2:E6">
+    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid time.&#10;HH:mm:ss" prompt="Required field" sqref="E2:E6">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>

--- a/src/Excelsior.Tests/TypeInferenceTests.TemplateInfersDateValidation.verified.xlsx
+++ b/src/Excelsior.Tests/TypeInferenceTests.TemplateInfersDateValidation.verified.xlsx
@@ -134,23 +134,23 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="6">
-    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time.&#10;yyyy-MM-dd HH:mm:ss" prompt="Required field" sqref="A2:A6">
+    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time.&#10;yyyy-MM-dd HH:mm:ss" prompt="Date and time as yyyy-MM-dd HH:mm:ss" sqref="A2:A6">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time.&#10;yyyy-MM-dd HH:mm:ss z" prompt="Required field" sqref="B2:B6">
+    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time.&#10;yyyy-MM-dd HH:mm:ss z" prompt="Date and time as yyyy-MM-dd HH:mm:ss z" sqref="B2:B6">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date.&#10;yyyy-MM-dd" prompt="Required field" sqref="C2:C6">
+    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date.&#10;yyyy-MM-dd" prompt="Date as yyyy-MM-dd" sqref="C2:C6">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date.&#10;yyyy-MM-dd" sqref="D2:D6">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date.&#10;yyyy-MM-dd" prompt="Date as yyyy-MM-dd" sqref="D2:D6">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid time.&#10;HH:mm:ss" prompt="Required field" sqref="E2:E6">
+    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid time.&#10;HH:mm:ss" prompt="Time as HH:mm:ss" sqref="E2:E6">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>

--- a/src/Excelsior.Tests/TypeInferenceTests.TemplateInfersDateValidation.verified.xlsx
+++ b/src/Excelsior.Tests/TypeInferenceTests.TemplateInfersDateValidation.verified.xlsx
@@ -9,9 +9,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-MM-dd HH:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="yyyy-MM-dd"/>
+    <numFmt numFmtId="165" formatCode="yyyy-MM-dd HH:mm:ss z"/>
+    <numFmt numFmtId="166" formatCode="yyyy-MM-dd"/>
+    <numFmt numFmtId="167" formatCode="HH:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -41,11 +43,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0"/>
     <xf fontId="1" fillId="0" borderId="0" applyFont="1" applyFill="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFont="0" applyFill="0"/>
   </cellXfs>
   <dxfs count="1">
     <dxf>
@@ -63,9 +67,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="13" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9" style="3" customWidth="1"/>
-    <col min="3" max="3" width="16" style="3" customWidth="1"/>
-    <col min="4" max="4" width="11" style="2" customWidth="1"/>
+    <col min="2" max="2" width="10" style="3" customWidth="1"/>
+    <col min="3" max="3" width="9" style="4" customWidth="1"/>
+    <col min="4" max="4" width="16" style="4" customWidth="1"/>
+    <col min="5" max="5" width="9" style="5" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -76,22 +82,32 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Day</t>
+          <t xml:space="preserve">Offset</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Day</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t xml:space="preserve">OptionalDay</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clock</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Bounded</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D1"/>
+  <autoFilter ref="A1:F1"/>
   <conditionalFormatting sqref="A2:A6">
     <cfRule type="containsBlanks" dxfId="0" priority="1">
       <formula>LEN(TRIM(A2))=0</formula>
@@ -102,25 +118,43 @@
       <formula>LEN(TRIM(B2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D6">
+  <conditionalFormatting sqref="C2:C6">
     <cfRule type="containsBlanks" dxfId="0" priority="3">
-      <formula>LEN(TRIM(D2))=0</formula>
+      <formula>LEN(TRIM(C2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
-    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date." prompt="Required field" sqref="A2:A6">
+  <conditionalFormatting sqref="E2:E6">
+    <cfRule type="containsBlanks" dxfId="0" priority="4">
+      <formula>LEN(TRIM(E2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:F6">
+    <cfRule type="containsBlanks" dxfId="0" priority="5">
+      <formula>LEN(TRIM(F2))=0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="6">
+    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time.&#10;yyyy-MM-dd HH:mm:ss" prompt="Date and time as yyyy-MM-dd HH:mm:ss" sqref="A2:A6">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date." prompt="Required field" sqref="B2:B6">
+    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time.&#10;yyyy-MM-dd HH:mm:ss z" prompt="Date and time as yyyy-MM-dd HH:mm:ss z" sqref="B2:B6">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date." sqref="C2:C6">
+    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date.&#10;yyyy-MM-dd" prompt="Date as yyyy-MM-dd" sqref="C2:C6">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a date between 2020-01-01 and 2020-12-31." prompt="Date between 2020-01-01 and 2020-12-31" sqref="D2:D6">
+    <dataValidation type="date" operator="between" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date.&#10;yyyy-MM-dd" prompt="Date as yyyy-MM-dd" sqref="D2:D6">
+      <formula1>2</formula1>
+      <formula2>2958465</formula2>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid time.&#10;HH:mm:ss" prompt="Time as HH:mm:ss" sqref="E2:E6">
+      <formula1>2</formula1>
+      <formula2>2958465</formula2>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a date between 2020-01-01 and 2020-12-31." prompt="Date between 2020-01-01 and 2020-12-31" sqref="F2:F6">
       <formula1>43831</formula1>
       <formula2>44196</formula2>
     </dataValidation>
@@ -132,9 +166,11 @@
 <columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
   <sheet name="Events">
     <column index="1" property="Timestamp"/>
-    <column index="2" property="Day"/>
-    <column index="3" property="OptionalDay"/>
-    <column index="4" property="Bounded"/>
+    <column index="2" property="Offset"/>
+    <column index="3" property="Day"/>
+    <column index="4" property="OptionalDay"/>
+    <column index="5" property="Clock"/>
+    <column index="6" property="Bounded"/>
   </sheet>
 </columnMetadata>
 </file>
--- a/src/Excelsior.Tests/TypeInferenceTests.TemplateInfersDateValidation.verified.xlsx
+++ b/src/Excelsior.Tests/TypeInferenceTests.TemplateInfersDateValidation.verified.xlsx
@@ -11,7 +11,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-MM-dd HH:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="yyyy-MM-dd HH:mm:ss z"/>
+    <numFmt numFmtId="165" formatCode="yyyy-MM-dd HH:mm:ss zzz"/>
     <numFmt numFmtId="166" formatCode="yyyy-MM-dd"/>
     <numFmt numFmtId="167" formatCode="HH:mm:ss"/>
   </numFmts>
@@ -138,7 +138,7 @@
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time.&#10;yyyy-MM-dd HH:mm:ss z" prompt="Date and time as yyyy-MM-dd HH:mm:ss z" sqref="B2:B6">
+    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a valid date and time.&#10;yyyy-MM-dd HH:mm:ss zzz" prompt="Date and time as yyyy-MM-dd HH:mm:ss zzz" sqref="B2:B6">
       <formula1>2</formula1>
       <formula2>2958465</formula2>
     </dataValidation>

--- a/src/Excelsior.Tests/TypeInferenceTests.TemplateInfersDateValidation.verified.xlsx
+++ b/src/Excelsior.Tests/TypeInferenceTests.TemplateInfersDateValidation.verified.xlsx
@@ -163,7 +163,7 @@
 </file>
 
 <file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
-<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+<columnMetadata xmlns="https://github.com/Papyrine/Excelsior/columnMetadata/v1">
   <sheet name="Events">
     <column index="1" property="Timestamp"/>
     <column index="2" property="Offset"/>
